--- a/v1/dashboard_hanh_dong_v1.xlsx
+++ b/v1/dashboard_hanh_dong_v1.xlsx
@@ -638,7 +638,11 @@
           <t>Sản phẩm AI (đúng 1)</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>VLearn — trợ lý hỗ trợ learner khi làm bài lab</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
@@ -647,7 +651,11 @@
           <t>Nhóm người dùng chính (đúng 1)</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Learner đang học lab, đã từng bị kẹt và phải tự xoay xở trong 7 ngày gần đây</t>
+        </is>
+      </c>
       <c r="C5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
@@ -656,7 +664,11 @@
           <t>Quy trình trong phạm vi #1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Gặp điểm kẹt (lỗi cài đặt môi trường ở bước 3 của bài lab)</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
@@ -665,7 +677,11 @@
           <t>Quy trình trong phạm vi #2</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Hỏi trợ lý AI tutor tích hợp</t>
+        </is>
+      </c>
       <c r="C7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -674,7 +690,11 @@
           <t>Quy trình trong phạm vi #3 (tuỳ chọn)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr"/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Đi tiếp bài lab</t>
+        </is>
+      </c>
       <c r="C8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
@@ -692,7 +712,11 @@
           <t>NGOÀI phạm vi (loại trừ rõ)</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Rollout toàn khoá học</t>
+        </is>
+      </c>
       <c r="C10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
@@ -701,7 +725,11 @@
           <t>Triệu chứng quan sát được</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr"/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Learner ít quay lại dùng AI tutor tích hợp sau lần đầu</t>
+        </is>
+      </c>
       <c r="C11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
@@ -710,7 +738,11 @@
           <t>Mức độ hiện tại (Usage / Pilot / Deployment / Adoption / Normalization)</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr"/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Usage — đã dùng thử AI tutor tích hợp</t>
+        </is>
+      </c>
       <c r="C12" s="7" t="inlineStr"/>
     </row>
   </sheetData>
@@ -780,7 +812,11 @@
           <t>Workflow: AI nằm ở bước nào, đã đổi cách làm chưa?</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>AI tutor có trong công cụ nhưng chưa rõ nằm ở bước nào trong quy trình xử lý điểm kẹt</t>
+        </is>
+      </c>
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr"/>
     </row>
@@ -793,8 +829,16 @@
           <t>Con người: ai dùng, ai né, vì sao?</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Learner dùng ít, có vẻ do chưa quen giao diện mới</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Quan sát: learner mở tutor rồi đóng lại sau vài giây ở một số phiên</t>
+        </is>
+      </c>
       <c r="E6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
@@ -819,7 +863,11 @@
           <t>Độ tin cậy: câu trả lời có nguồn, ngày cập nhật, cách báo lỗi?</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Câu trả lời của AI tutor chưa kèm nguồn tài liệu</t>
+        </is>
+      </c>
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr"/>
     </row>
@@ -872,8 +920,16 @@
           <t>Direction — hướng đi rõ chưa</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Mục tiêu rõ: giảm thời gian bị kẹt</t>
+        </is>
+      </c>
       <c r="D13" s="7" t="inlineStr"/>
       <c r="E13" s="7" t="inlineStr"/>
     </row>
@@ -883,8 +939,16 @@
           <t>Readiness — dữ liệu, quyền, governance, kỹ năng, ngân sách</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr"/>
-      <c r="C14" s="7" t="inlineStr"/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>THIẾU</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Chưa rà lại tài liệu lab</t>
+        </is>
+      </c>
       <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="7" t="inlineStr"/>
     </row>
@@ -942,8 +1006,16 @@
           <t>AI hỗ trợ — người kiểm (tìm / tóm tắt / tạo nháp)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr"/>
-      <c r="C20" s="7" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>AI trả lời câu hỏi của learner</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Learner tự đọc và tự quyết định</t>
+        </is>
+      </c>
       <c r="D20" s="7" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr"/>
     </row>
@@ -1009,10 +1081,26 @@
           <t>Desire — muốn dùng / tin tưởng</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr"/>
-      <c r="C26" s="7" t="inlineStr"/>
-      <c r="D26" s="7" t="inlineStr"/>
-      <c r="E26" s="7" t="inlineStr"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Learner chưa quen dùng tutor tích hợp</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Quan sát: một số phiên đóng tutor sau &lt;10 giây</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Dự kiến: làm hướng dẫn sử dụng tutor</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -1130,11 +1218,29 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr"/>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
+      <c r="A5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Learner chưa quen dùng AI tutor tích hợp nên ít dùng lại</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>5 câu hỏi chẩn đoán (trục Con người)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Quan sát: một số phiên learner mở tutor rồi đóng lại sau vài giây</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Ít người quay lại dùng lần 2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1230,12 +1336,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr"/>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Gặp điểm kẹt ở bước 3 (cài đặt môi trường)</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Learner tự tìm, hỏi AI ngoài hoặc đồng đội</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Tìm file → hỏi đồng nghiệp → hỏi AI tutor tích hợp → đi tiếp</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>&lt;chưa xác định&gt;</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>&lt;chưa xác định&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>&lt;chưa xác định&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr"/>
@@ -1374,7 +1504,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>&lt;tên&gt;</t>
+          <t>Product owner</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -1389,7 +1519,11 @@
           <t>31–60 ngày</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Mở rộng thêm tính năng tutor</t>
+        </is>
+      </c>
       <c r="C5" s="7" t="inlineStr"/>
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr"/>
@@ -1400,7 +1534,11 @@
           <t>61–90 ngày</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Đánh giá hiệu quả tổng thể</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="inlineStr"/>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr"/>
@@ -1544,14 +1682,46 @@
           <t>Workflow</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Thời gian tiết kiệm (tự khai của learner)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>&lt;đo hiện trạng&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>&lt;mục tiêu nhóm&gt;</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Khảo sát tự khai</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>&lt;tên&gt;</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Gửi thông báo khuyến khích dùng nhiều hơn</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr"/>
@@ -1650,7 +1820,11 @@
           <t>Quyết định: TIẾP TỤC / SỬA / DỪNG</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>SỬA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1658,7 +1832,11 @@
           <t>Lý do (dựa trên bằng chứng nào)</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Lượt mở trợ giúp còn thấp, cần xem lại thiết kế trước khi mở rộng</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1666,7 +1844,11 @@
           <t>Điều kiện / cổng kế tiếp</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Chờ nhóm quyết định thêm hướng dẫn sử dụng</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1674,7 +1856,11 @@
           <t>Bước tiếp theo (ai, khi nào)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Chưa xác định owner và mốc thời gian cụ thể</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/v1/dashboard_hanh_dong_v1.xlsx
+++ b/v1/dashboard_hanh_dong_v1.xlsx
@@ -35,24 +35,25 @@
     <font>
       <b val="1"/>
       <color rgb="001F3864"/>
-      <sz val="11"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -104,29 +105,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,11 +491,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B14"/>
+  <dimension ref="B1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,83 +508,93 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Day 28 Track 01 · Nhóm: &lt;TÊN NHÓM&gt;</t>
+          <t>Day 28 Track 01 · Nhóm 333 · Thành viên: Nguyễn Hoàng Minh, Nguyễn Việt Hải, Trịnh Hải Đăng</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Cách dùng workbook này:</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Bản v1 là bản nhóm làm trước khi kiểm tra chéo, để đối chiếu.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1_Pham_vi      → khoá 1 sản phẩm AI · 1 nhóm người dùng · 2–4 quy trình</t>
-        </is>
-      </c>
+      <c r="B5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2_Chan_doan    → 5 câu hỏi chẩn đoán + Gartner-Lite + Mollick + ADKAR</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Các sheet trong workbook này:</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3_Nguyen_nhan  → 1–2 nguyên nhân gốc, mỗi cái gắn framework + ≥1 bằng chứng</t>
+          <t>1_Pham_vi: khoá một sản phẩm AI, một nhóm người dùng, bốn bước quy trình.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4_Workflow     → AS-IS / TO-BE + nguồn kiểm chứng + owner + xử lý khi AI sai</t>
+          <t>2_Chan_doan: năm câu hỏi chẩn đoán, Gartner-Lite, phân chia việc Mollick, ADKAR.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5_Lo_trinh     → 30–60–90 ngày, mỗi cổng có owner + dấu hiệu hoàn thành</t>
+          <t>3_Nguyen_nhan_goc: hai nguyên nhân gốc, mỗi cái gắn framework và bằng chứng.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6_Chi_so       → ≥1 product metric + ≥1 workflow metric, đủ 6 cột bắt buộc</t>
+          <t>4_Workflow_ASIS_TOBE: quy trình cũ và quy trình mới, kèm nguồn kiểm chứng, người chịu trách nhiệm, cách xử lý khi AI không chắc.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7_Quyet_dinh   → tiếp tục / sửa / dừng + lý do + bước tiếp theo</t>
+          <t>5_Lo_trinh_30_60_90: ba cổng quyết định dựa trên bằng chứng, mỗi cổng có owner và dấu hiệu hoàn thành.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>6_Chi_so: chỉ số cấp sản phẩm và cấp quy trình, mỗi chỉ số đủ baseline, target, nguồn, người phụ trách, hành động khi số liệu xấu.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Nguyên tắc chấm: phạm vi có cụ thể không · nguyên nhân có căn cứ không · mỗi chỉ số có dẫn tới một quyết định không.</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>7_Quyet_dinh: tiếp tục, sửa hay dừng, kèm lý do và bước tiếp theo.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Ứng dụng thật bắt đầu khi CÔNG VIỆC + TRÁCH NHIỆM + CÁCH KIỂM SOÁT đã thay đổi.</t>
+      <c r="B14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Nguyên tắc chấm: phạm vi có cụ thể không, nguyên nhân có căn cứ không, mỗi chỉ số có dẫn tới một quyết định không.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ứng dụng thật bắt đầu khi công việc, trách nhiệm và cách kiểm soát đã thay đổi.</t>
         </is>
       </c>
     </row>
@@ -603,147 +612,159 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>CHẶNG 1 — KHOÁ PHẠM VI</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Mục</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Nội dung (điền)</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Ghi chú / vì sao chọn</t>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Ghi chú, vì sao chọn</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Sản phẩm AI (đúng 1)</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>VLearn — trợ lý hỗ trợ learner khi làm bài lab</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr"/>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>VLearn, trợ lý AI tích hợp trong nền tảng học, hỗ trợ learner ngay khi đang làm bài lab.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm chọn một sản phẩm để chẩn đoán được sâu, không nói chung về AI trong nền tảng.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Nhóm người dùng chính (đúng 1)</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Learner đang học lab, đã từng bị kẹt và phải tự xoay xở trong 7 ngày gần đây</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Learner đang theo học lab của VLearn, cụ thể là những người đã bị kẹt ở bước cài đặt môi trường và phải tự xoay xở trong bảy ngày gần đây.</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm khoanh vào nhóm learner có va chạm thật với vấn đề.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Quy trình trong phạm vi #1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Gặp điểm kẹt (lỗi cài đặt môi trường ở bước 3 của bài lab)</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Learner nhận ra mình bị kẹt khi làm một bước của bài lab.</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Quy trình trong phạm vi #2</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Hỏi trợ lý AI tutor tích hợp</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Learner hỏi trợ lý AI về điểm kẹt đó.</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Quy trình trong phạm vi #3 (tuỳ chọn)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Đi tiếp bài lab</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Learner kiểm chứng câu trả lời của trợ lý với tài liệu lab.</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Quy trình trong phạm vi #4 (tuỳ chọn)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Learner quyết định làm theo hướng dẫn hoặc chuyển việc cho coach.</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>NGOÀI phạm vi (loại trừ rõ)</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Rollout toàn khoá học</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm không xét việc rollout cho toàn khoá học, không xét việc để AI tự phán đoán đúng sai thay learner, và không xét các điểm kẹt khác ngoài lỗi cài đặt môi trường ở bước ba của bài lab đang chọn.</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Triệu chứng quan sát được</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Learner ít quay lại dùng AI tutor tích hợp sau lần đầu</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Learner đã có trợ lý AI tích hợp nhưng vẫn rời nền tảng, mở Claude hoặc ChatGPT để hỏi lại và tự kiểm chứng. Nhiều phiên làm lab bị kéo dài hoặc bỏ dở ngay ở bước cài đặt môi trường.</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Mức độ hiện tại (Usage / Pilot / Deployment / Adoption / Normalization)</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Usage — đã dùng thử AI tutor tích hợp</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Usage. Learner tự dùng trợ lý theo cách riêng, quy trình lab chưa ghi nhận bước hỏi trợ lý, chưa có người chịu trách nhiệm cho chất lượng câu trả lời.</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -756,384 +777,543 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>CHẶNG 1 — CHẨN ĐOÁN</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>A. Năm câu hỏi chẩn đoán</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Câu hỏi</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Phát hiện (điền)</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Phát hiện</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Bằng chứng</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Workflow: AI nằm ở bước nào, đã đổi cách làm chưa?</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>AI tutor có trong công cụ nhưng chưa rõ nằm ở bước nào trong quy trình xử lý điểm kẹt</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Trợ lý AI nằm ngoài chuỗi bước chính thức của bài lab. Learner có thể mở trợ lý nhưng bước hỏi trợ lý và bước kiểm chứng chưa được ghi vào quy trình, và không có bước chuyển việc cho coach. Đây là một nguyên nhân gốc.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm quan sát một phiên làm lab của thành viên trong nhóm. Learner mở trợ lý rồi vẫn quay lại dò tay từng dòng hướng dẫn, không có chỗ nào trong quy trình nhắc gọi coach.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Con người: ai dùng, ai né, vì sao?</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Learner dùng ít, có vẻ do chưa quen giao diện mới</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Quan sát: learner mở tutor rồi đóng lại sau vài giây ở một số phiên</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Learner không thiếu kỹ năng bấm và gõ câu hỏi. Cái learner thiếu là căn cứ để tin câu trả lời, vì trợ lý gộp phần có trong tài liệu lab và phần tự suy đoán vào cùng một câu trả lời.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Learner nói lại nguyên văn: Anh chụp cái slide lên hỏi, nó trả lời trơn tru, nhưng anh không biết chỗ nào lấy từ bài, chỗ nào nó tự nghĩ, nên anh buộc phải tin thôi.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Mức sẵn sàng: dữ liệu / quyền / governance / kỹ năng / ngân sách?</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Bộ tài liệu lab có sẵn nhưng chưa có người chịu trách nhiệm giữ bản mới nhất và chưa có lịch cập nhật. Quyền đọc log phiên học và phần learner đồng ý cho ghi log chưa được xác nhận.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Khi nhóm hỏi ai là người sở hữu nội dung lab, không ai trong buổi trả lời được.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Độ tin cậy: câu trả lời có nguồn, ngày cập nhật, cách báo lỗi?</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Câu trả lời của AI tutor chưa kèm nguồn tài liệu</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Câu trả lời của trợ lý không kèm trích nguồn, không đánh dấu phần nằm ngoài tài liệu, và không có nút báo sai hay chuyển người. Khi trợ lý trả lời lệch, hệ thống không phát hiện. Đây là một nguyên nhân gốc.</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Các lần nhóm tự thử hỏi trợ lý đều cho câu trả lời không kèm nguồn.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Cách đo lường: đang đo gì, chỉ số có dẫn tới quyết định không?</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>B. Gartner-Lite (chạy TRƯỚC khi mở rộng)</t>
-        </is>
-      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Nền tảng hiện chỉ đếm số lượt learner mở trợ lý và số câu hỏi gửi lên. Nền tảng chưa đo thời gian xử lý một điểm kẹt, tỷ lệ learner phải làm lại, hay tỷ lệ câu trả lời kiểm chứng được.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Bảng số liệu learner mà nhóm được xem chỉ có cột lượt dùng, không có cột thời gian hay chất lượng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Kết luận</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm sửa độ tin cậy trong lượt trả lời và đưa hai bước hỏi trợ lý cùng chuyển coach vào quy trình lab, trước khi tìm cách tăng số lượt dùng.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>B. Gartner-Lite, chạy trước khi mở rộng</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Trục</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Đánh giá (ĐẠT / THIẾU)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Đánh giá</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Bằng chứng</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Hàm ý (pilot sửa gì / rollout được chưa)</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Direction — hướng đi rõ chưa</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Hàm ý</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Direction, hướng đi đã rõ chưa</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Mục tiêu rõ: giảm thời gian bị kẹt</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Readiness — dữ liệu, quyền, governance, kỹ năng, ngân sách</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Mục tiêu của nhóm rõ: rút ngắn thời gian learner tự xử lý một điểm kẹt khi làm lab và giảm số phiên bỏ dở. Người dùng, giá trị và phạm vi đã được khoá ở bước trên.</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Hướng đi đủ rõ để chạy một pilot nhỏ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Readiness, gồm dữ liệu, quyền, governance, kỹ năng, ngân sách</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>THIẾU</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Chưa rà lại tài liệu lab</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Absorption — owner, hỗ trợ vận hành, cơ chế học từ lỗi</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr"/>
-      <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Tài liệu lab chưa có người phụ trách và lịch cập nhật. Quyền đọc log phiên học và phần learner đồng ý chưa xác nhận. Ngân sách cho việc chấm chất lượng câu trả lời chưa có.</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm chạy pilot nhỏ để vá các thiếu hụt này, chưa mở rộng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Absorption, gồm owner, hỗ trợ vận hành, cơ chế học từ lỗi</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>THIẾU</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Chưa có người chịu trách nhiệm cho chất lượng câu trả lời của trợ lý. Chưa có kênh để learner báo câu trả lời sai. Chưa có vòng xem lại lỗi hàng tuần.</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm phải lập một người phụ trách QA và một kênh phản hồi trước khi tính chuyện nhân rộng.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>C. Mollick — phân chia việc</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Vùng</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Tác vụ cụ thể trong quy trình (điền)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Ai giữ quyền / chịu trách nhiệm</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
+          <t>Kết luận</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm chạy pilot nhỏ trong một nhóm learner và một bài lab để vá phần readiness và absorption.</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Người giữ quyền (phê duyệt cuối, ngoại lệ)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr"/>
-      <c r="C19" s="7" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr"/>
+          <t>C. Mollick, phân chia việc giữa người và AI</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>AI hỗ trợ — người kiểm (tìm / tóm tắt / tạo nháp)</t>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Vùng</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>AI trả lời câu hỏi của learner</t>
+          <t>Tác vụ cụ thể trong quy trình</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Learner tự đọc và tự quyết định</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr"/>
+          <t>Ai giữ quyền, chịu trách nhiệm</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>AI tự động (lặp lại, rủi ro thấp, có tiêu chí kiểm tra)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr"/>
-      <c r="C21" s="7" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="7" t="inlineStr"/>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Người giữ quyền, phê duyệt cuối và xử lý ngoại lệ</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Learner đọc lại nguồn mà trợ lý trích, đối chiếu với bài lab, rồi quyết định làm theo hay chuyển coach. Coach chịu trách nhiệm cuối cho các điểm kẹt mà trợ lý ghi là không đủ căn cứ.</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Learner cho phần tự làm, coach cho phần chuyển giao.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>AI hỗ trợ, người kiểm: trợ lý tìm, tóm tắt, tạo nháp</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Trợ lý tìm trong tài liệu lab, tóm tắt bước learner đang vướng, và soạn câu trả lời nháp có trích dẫn từng ý.</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Trợ lý làm nháp, learner kiểm chứng trước khi làm theo.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>D. ADKAR — tìm điểm nghẽn ở người dùng</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Bước</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Có nghẽn? (Có / Không)</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Mô tả điểm nghẽn (điền)</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Bằng chứng</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Việc cần làm (KHÔNG mặc định mở lớp đào tạo)</t>
+          <t>AI tự động, chỉ với tác vụ lặp lại, rủi ro thấp, có tiêu chí kiểm tra</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Trợ lý tự đánh giá câu trả lời của mình đáng tin đến mức nào và gợi ý learner có nên tin hay không. Nhóm chưa tách rõ phần này với phần learner tự quyết.</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Chưa chốt, còn lẫn giữa Option B và Option C.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Awareness — biết có công cụ</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr"/>
-      <c r="C25" s="7" t="inlineStr"/>
-      <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr"/>
+          <t>D. ADKAR, tìm điểm nghẽn ở người dùng</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>Desire — muốn dùng / tin tưởng</t>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Bước</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
+          <t>Có nghẽn</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Mô tả điểm nghẽn</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Bằng chứng</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Việc cần làm, không mặc định mở lớp đào tạo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Awareness, biết có công cụ</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Có, một phần</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Learner biết có trợ lý nhưng chưa rõ nên dùng cho loại câu hỏi nào, nên vẫn tự chọn giữa trợ lý tích hợp và công cụ ngoài theo cảm tính.</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Learner kể là tự chọn giữa trợ lý và ChatGPT tuỳ lúc.</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm ghi rõ trong quy trình lab loại điểm kẹt nào nên hỏi trợ lý trước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Desire, muốn dùng và tin tưởng</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Learner chưa quen dùng tutor tích hợp</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Quan sát: một số phiên đóng tutor sau &lt;10 giây</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Dự kiến: làm hướng dẫn sử dụng tutor</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Knowledge — biết cách dùng</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr"/>
-      <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Ability — làm được trong việc thật</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr"/>
-      <c r="C28" s="7" t="inlineStr"/>
-      <c r="D28" s="7" t="inlineStr"/>
-      <c r="E28" s="7" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Learner ngại tin câu trả lời vì không nhìn thấy nguồn, nên hoặc tin hết hoặc bỏ qua và tự xoay.</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Câu learner nói: buộc phải tin thôi.</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm bật trích nguồn và đánh dấu phần ngoài tài liệu. Mở lớp đào tạo không xử lý được điểm nghẽn này.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Reinforcement — được củng cố, không quay lại cách cũ</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr"/>
-      <c r="C29" s="7" t="inlineStr"/>
-      <c r="D29" s="7" t="inlineStr"/>
-      <c r="E29" s="7" t="inlineStr"/>
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge, biết cách dùng</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Cần làm</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Learner chưa quen cách hỏi để trợ lý trả về đúng đoạn tài liệu, và chưa quen cách đối chiếu nguồn.</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm quan sát learner hỏi câu rất chung rồi nhận câu trả lời chung.</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm thêm một hướng dẫn ngắn ngay trong màn hình trợ lý.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Ability, làm được trong việc thật</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Cần làm</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm chưa thử quy trình mới trên một phiên làm lab thật đầy đủ, mới dừng ở ba phiên thử ngắn.</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Ba phiên thử của nhóm chỉ tập trung vào việc chọn option, chưa chạy hết một bài lab.</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm chạy thử với vài learner, có coach ngồi cạnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Reinforcement, được củng cố và không quay lại cách cũ</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Cần làm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Chưa có phản hồi khi learner báo câu trả lời sai. Chưa ai theo dõi hành vi learner rời nền tảng.</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Log rời nền tảng hiện không ai xem.</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm thêm nút báo sai và xem log rời nền tảng hàng tuần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Kết luận</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr"/>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Đào tạo là chưa đủ. Nhóm phải sửa trong lượt trả lời của trợ lý và trong quy trình lab.</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1150,95 +1330,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>CHẶNG 1 — CHỐT 1–2 NGUYÊN NHÂN GỐC (mỗi cái ≥1 bằng chứng)</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>CHẶNG 1 — HAI NGUYÊN NHÂN GỐC, MỖI CÁI CÓ ÍT NHẤT MỘT BẰNG CHỨNG</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Nguyên nhân gốc (không phải triệu chứng)</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Framework xác định (5 câu hỏi / Gartner-Lite / Mollick / ADKAR)</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Bằng chứng (≥1, cụ thể)</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Nguyên nhân gốc, không phải triệu chứng</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Framework xác định</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Bằng chứng cụ thể</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Triệu chứng nó giải thích</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>vd</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Câu trả lời không kèm nguồn + ngày cập nhật nên người dùng không dám tin</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>5 câu hỏi #4 (độ tin cậy) + ADKAR: Desire</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Phỏng vấn 6/8 người: 'không biết số này lấy từ đâu'; log: 70% phiên bỏ giữa chừng</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Ít người quay lại dùng lần 2</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Độ tin cậy chưa được thiết kế trong lượt trả lời. Trợ lý gộp phần có trong tài liệu lab và phần tự suy đoán, không trích nguồn, không đánh dấu phần ngoài tài liệu, và không có đường báo sai. Learner không phân biệt được nên hoặc tin hết hoặc bỏ qua.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Năm câu hỏi chẩn đoán, trục Tin cậy.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Learner nói buộc phải tin thôi vì không biết chỗ nào trợ lý lấy từ bài.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Learner rời nền tảng đi hỏi công cụ ngoài, phiên làm lab kéo dài.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Learner chưa quen dùng AI tutor tích hợp nên ít dùng lại</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>5 câu hỏi chẩn đoán (trục Con người)</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Quan sát: một số phiên learner mở tutor rồi đóng lại sau vài giây</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Ít người quay lại dùng lần 2</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Quy trình lab không có bước hỏi trợ lý và không có đường chuyển coach ít ma sát. Khi trợ lý không đủ căn cứ, learner không biết chuyển việc cho ai nên tự dò tay hoặc bỏ dở.</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Năm câu hỏi chẩn đoán, trục Workflow.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm quan sát một phiên làm lab, learner mở trợ lý rồi vẫn dò tay từng dòng.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Số phiên bỏ dở ở bước cài đặt môi trường.</t>
         </is>
       </c>
     </row>
@@ -1253,183 +1435,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>CHẶNG 2 — VẼ LẠI QUY TRÌNH (mỗi quy trình 1 bảng)</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>CHẶNG 2 — QUY TRÌNH XỬ LÝ MỘT ĐIỂM KẸT KHI LÀM LAB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Quy trình / Bước</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>AS-IS (hiện tại)</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>TO-BE (sau thiết kế lại)</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Bước</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>AS-IS, hiện tại</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>TO-BE, sau thiết kế lại</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Nguồn kiểm chứng</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Người chịu trách nhiệm kết quả cuối</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Xử lý khi AI không chắc chắn</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Tra cứu chính sách</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Tìm file → hỏi đồng nghiệp → đọc tài liệu</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Hỏi AI → xem nguồn + ngày → người kiểm chứng → dùng / báo lỗi</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Kho tài liệu chính thức vX</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Chuyên viên xử lý hồ sơ</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>AI trả 'không đủ dữ kiện' → chuyển người phụ trách trong 1 giờ</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Bước 1. Nhận ra điểm kẹt</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Learner đọc thông báo lỗi rồi tự đoán nguyên nhân.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Learner mở trợ lý ngay tại bước lab đang làm và dán thông báo lỗi vào.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Bài lab đang mở trên nền tảng.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Learner.</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Không áp dụng ở bước này.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Gặp điểm kẹt ở bước 3 (cài đặt môi trường)</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Learner tự tìm, hỏi AI ngoài hoặc đồng đội</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Tìm file → hỏi đồng nghiệp → hỏi AI tutor tích hợp → đi tiếp</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>&lt;chưa xác định&gt;</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>&lt;chưa xác định&gt;</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>&lt;chưa xác định&gt;</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Bước 2. Tìm câu trả lời</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Learner tìm trong slide, hỏi bạn, hoặc mở ChatGPT ngoài nền tảng.</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Trợ lý tìm trong tài liệu lab, trả lời kèm trích dẫn từng ý và đánh dấu phần nằm ngoài tài liệu.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Bộ tài liệu lab bản mới nhất do data owner giữ.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Data owner giữ nguồn, trợ lý tạo nháp.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Trợ lý ghi rõ phần nào không tìm thấy trong tài liệu.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr"/>
-      <c r="B6" s="7" t="inlineStr"/>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Bước 3. Kiểm chứng</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Learner khó biết bản tài liệu nào mới nhất nên gần như không đối chiếu.</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Learner mở đúng đoạn nguồn trợ lý trích và đối chiếu trước khi làm theo.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Đoạn tài liệu lab mà trợ lý trích dẫn.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Learner.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Nếu learner đối chiếu thấy lệch, learner bấm chuyển coach.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Bước 4. Quyết định</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Learner làm theo mà không chắc, hoặc bỏ dở phiên học.</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Nếu nguồn khớp, learner làm theo. Nếu trợ lý ghi không đủ căn cứ hoặc learner thấy lệch, learner chuyển coach.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Kết quả bước lab trên hệ thống.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Learner cho phần tự làm, coach cho phần chuyển giao.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Trợ lý tự gắn nhãn không đủ căn cứ, ẩn nút làm theo, hiện nút chuyển coach. Coach nhận trong hàng chờ và phản hồi trong khung giờ hỗ trợ.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr"/>
-      <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr"/>
-      <c r="B10" s="7" t="inlineStr"/>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr"/>
-      <c r="B11" s="7" t="inlineStr"/>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr"/>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Ghi chú bản v1</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Đường chuyển coach ở bản v1 mới nêu ý tưởng, chưa ghi rõ nhãn không đủ căn cứ và hàng chờ hỗ trợ.</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1446,102 +1644,126 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>CHẶNG 2 — LỘ TRÌNH 30–60–90 (ba CỔNG dựa trên bằng chứng, không phải lịch cứng)</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>CHẶNG 2 — LỘ TRÌNH 30–60–90, BA CỔNG DỰA TRÊN BẰNG CHỨNG</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Giai đoạn</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Mục tiêu giai đoạn</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Hành động chính</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Dấu hiệu HOÀN THÀNH (điều kiện mở cổng sang giai đoạn sau)</t>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Dấu hiệu hoàn thành, điều kiện mở cổng sau</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>0–30 ngày</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Sửa readiness + có baseline</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Gắn nguồn vào câu trả lời; lập data owner; đo hiện trạng</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Có mốc ban đầu + data owner → mới sang giai đoạn 2</t>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Chứng minh vấn đề có thật và lấy được số liệu nền.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm vẽ AS-IS và TO-BE. Nhóm khoá bộ tài liệu lab dùng cho pilot. Nhóm chỉ định data owner. Nhóm ghi baseline tuần đầu cho thời gian xử lý một điểm kẹt, tỷ lệ phiên bỏ dở và tỷ lệ rời nền tảng.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Product owner của trợ lý cùng data owner tài liệu lab.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Có log quy trình, có mẫu câu hỏi thật, có baseline. Nếu chưa lấy được số liệu thì nhóm sửa cách ghi log trước, chưa chuyển sang giai đoạn hai.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>31–60 ngày</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Mở rộng thêm tính năng tutor</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Chứng minh chất lượng câu trả lời và đường bàn giao.</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm bật trích nguồn và nhãn phần ngoài tài liệu. Nhóm chấm QA trên mẫu phiên thật hàng tuần. Nhóm thêm nút chuyển coach và hàng chờ. Nhóm thêm hướng dẫn ngắn trong màn hình trợ lý.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Người phụ trách QA cùng lab coach.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Tỷ lệ câu trả lời trích nguồn đúng và tỷ lệ learner hoàn thành bước lab mà không phải làm lại đạt mức nhóm đặt. Nếu số liệu xấu, nhóm tăng cỡ mẫu QA và thu hẹp bộ tài liệu.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>61–90 ngày</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Đánh giá hiệu quả tổng thể</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Quyết định có mở rộng hay không.</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm so kết quả với baseline. Nhóm chốt người vận hành thường trực. Nhóm kiểm tra quyền truy cập và phần learner đồng ý ghi log. Nhóm xem lại chi phí.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Product owner cùng người phụ trách governance.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Chất lượng, hành vi và kết quả bước lab cùng đạt ngưỡng thì nhóm mới mở sang bài lab hoặc nhóm learner khác. Nếu không đạt, nhóm sửa hoặc dừng pilot.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1554,240 +1776,334 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>CHẶNG 2 — DASHBOARD CHỈ SỐ · ≥1 product metric + ≥1 workflow metric · mỗi chỉ số đủ 6 cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Nhắc: 5 tầng đo = Sử dụng → Hành vi → Năng suất → Chất lượng &amp; độ tin cậy → Giá trị. Ưu tiên decision metric hơn activity metric.</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>CHẶNG 2 — DASHBOARD CHỈ SỐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Năm tầng đo: sử dụng, hành vi, năng suất, chất lượng và độ tin cậy, giá trị. Nhóm theo dõi từ dưới lên và ra quyết định dựa trên giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Cấp</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Tên chỉ số</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Tầng đo</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Loại</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Nguồn dữ liệu</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Người phụ trách</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Hành động khi chỉ số xấu</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Cấp (Product / Workflow)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Tên chỉ số</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Tầng đo (1–5)</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Loại (activity / decision)</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Nguồn dữ liệu</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Người phụ trách</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Hành động khi chỉ số XẤU</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Số lượt learner mở trợ lý mỗi tuần</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Hoạt động</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Đo tuần đầu</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Tăng so với tuần đầu</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Log nền tảng</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Trưởng nhóm lab</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Nhắc learner dùng trợ lý nhiều hơn.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Tỷ lệ câu trả lời có nguồn kiểm chứng</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>decision</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>&lt;đo hiện trạng&gt;</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>&lt;mục tiêu nhóm&gt;</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>QA mẫu hằng tuần</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>&lt;tên&gt;</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Xem lại kiến trúc tin cậy: nguồn → trích nguồn → QA</t>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Số câu hỏi learner gửi cho trợ lý mỗi phiên</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Hoạt động</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Đo tuần đầu</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Tăng nhẹ</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Log nền tảng</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Trưởng nhóm lab</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Xem lại giao diện trợ lý.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Workflow</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Thời gian tiết kiệm (tự khai của learner)</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Thời gian learner tự khai là tiết kiệm được mỗi phiên</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>activity</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>&lt;đo hiện trạng&gt;</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>&lt;mục tiêu nhóm&gt;</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Khảo sát tự khai</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>&lt;tên&gt;</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Gửi thông báo khuyến khích dùng nhiều hơn</t>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Hoạt động</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Khảo sát nhanh cuối phiên</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Learner tự khai tiết kiệm nhiều hơn</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Khảo sát learner</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Chủ quy trình lab</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Hỏi thêm learner.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr"/>
-      <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Thời gian hoàn thành bước cài đặt môi trường</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Quyết định</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Đo hiện trạng từ log</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Giảm so với hiện trạng</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Log tác vụ</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Chủ quy trình lab</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Xem lại hướng dẫn của bước.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Tỷ lệ learner hoàn thành bài lab</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Quyết định</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Số hiện tại trên hệ thống</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Tăng</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Hệ thống lab</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Chủ nghiệp vụ khoá học</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Điều chỉnh nội dung lab.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr"/>
-      <c r="B10" s="7" t="inlineStr"/>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr"/>
-      <c r="B11" s="7" t="inlineStr"/>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr"/>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Ghi chú của nhóm</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Các chỉ số trên phần lớn là chỉ số hoạt động, chưa đủ mạnh để ra quyết định mở rộng. Nhóm sẽ bổ sung ở bản v2.</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1804,61 +2120,61 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>CHẶNG 3 — MEMO QUYẾT ĐỊNH (tóm tắt, chi tiết ở memo/memo_quyet_dinh.md)</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>CHẶNG 3 — QUYẾT ĐỊNH, chi tiết ở memo/memo_quyet_dinh.md</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Quyết định: TIẾP TỤC / SỬA / DỪNG</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>SỬA</t>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>TIẾP TỤC. Nhóm nghiêng về Option A và định pilot trong một nhóm learner.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Lý do (dựa trên bằng chứng nào)</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Lượt mở trợ giúp còn thấp, cần xem lại thiết kế trước khi mở rộng</t>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Ba phiên thử, tính cả phiên thứ ba, đều nghiêng về Option A.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Điều kiện / cổng kế tiếp</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Chờ nhóm quyết định thêm hướng dẫn sử dụng</t>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Chưa nêu rõ cổng.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Bước tiếp theo (ai, khi nào)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Chưa xác định owner và mốc thời gian cụ thể</t>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Nhóm sẽ làm rõ cách chia việc giữa người và AI, và bổ sung chỉ số.</t>
         </is>
       </c>
     </row>
